--- a/jobs/leads/2026-10-21.xlsx
+++ b/jobs/leads/2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$M$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$P$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -461,11 +461,14 @@
     <col width="15.5" customWidth="1" min="6" max="6"/>
     <col width="25.4" customWidth="1" min="7" max="7"/>
     <col width="17.3" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="21.8" customWidth="1" min="11" max="11"/>
+    <col width="48.8" customWidth="1" min="9" max="9"/>
+    <col width="16.4" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="21.8" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -511,25 +514,40 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Ένδειξη μεγέθους (πηγή)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Διαφημίσεις 24μ.</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Meta Ad Library</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Τι πρόσεξα</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Πού το είδα</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Υπηρεσία που ταιριάζει</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Opener</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Έγκριση</t>
         </is>
@@ -578,25 +596,40 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=oikotexnia.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>Το footer γράφει «Copyright 2020» και η αρχική δείχνει ακόμα την ενότητα «#MenoumeSpiti – Η οικοτεχνία λαμβάνει όλα τα απαραίτητα μέτρα προστασίας».</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>https://oikotexnia.gr/ — footer και ενότητα #MenoumeSpiti στην αρχική</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>E-shop / Meta Ads</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στην αρχική σας υπάρχει ακόμα το «#MenoumeSpiti» και footer του 2020 — πριν τα δώρα των Χριστουγέννων, θα σας έδειχνα πώς θα έμοιαζε ένα ανανεωμένο e-shop για τα γλυκά σας.</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr"/>
+      <c r="P2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -641,25 +674,40 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
+          <t>Φυσικό κατάστημα, Τζιραίων 16, Μακρυγιάννη (site)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=melissinos-art.com&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>Οι σελίδες προϊόντων δεν έχουν τιμή ούτε καλάθι, μόνο φόρμα «Send an enquiry»· το footer γράφει «© 2022 Melissinos Art».</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>https://melissinos-art.com/product/plato/ — σελίδα προϊόντος· footer της αρχικής</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>E-shop / Google Ads</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στο site σας τα σανδάλια δεν αγοράζονται online, μόνο με enquiry — κατά την δική μου επαγγελματική άποψη, ένα κανονικό checkout θα σας έφερνε πωλήσεις που τώρα χάνονται πριν τη Black Friday.</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -704,25 +752,40 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=esthique.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>Το site δεν έχει τιμές ούτε καλάθι· οι παραγγελίες γίνονται μόνο από την ενότητα «Τηλεφωνικές Παραγγελίες». Footer: «Esthique 2024».</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>https://www.esthique.gr/el — ενότητα «Τηλεφωνικές Παραγγελίες» και footer</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>E-shop / Meta Ads</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στο esthique.gr οι παραγγελίες γίνονται μόνο τηλεφωνικά — θα σας πρότεινα ένα απλό e-shop ώστε να πουλάτε και όταν δεν σηκώνετε το τηλέφωνο.</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -767,25 +830,40 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=happyhippie.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>Το footer γράφει «Copyright © 2017, HappyHippie.gr» και η ενότητα «ΑΥΤΟ ΤΟ ΜΗΝΑ ΠΡΟΤΕΙΝΟΥΜΕ» δείχνει προϊόντα με εικόνες από φάκελο του 2018.</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>https://www.happyhippie.gr/ — footer και ενότητα «ΑΥΤΟ ΤΟ ΜΗΝΑ ΠΡΟΤΕΙΝΟΥΜΕ»</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>E-shop / Meta Ads</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι το footer του happyhippie.gr γράφει ακόμα 2017 — αν σκέφτεστε ανανέωση του e-shop πριν τη νέα σεζόν βαπτίσεων, θα χαρώ να σας δείξω μια πρόταση.</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -830,25 +908,40 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=eshopgamouvaptisis.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>Η αρχική σελίδα εμφανίζει ακόμα το μήνυμα «This page require Adobe Flash 9.0 (or higher) plug in» — το Flash δεν υποστηρίζεται πια από τους browsers.</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>https://www.eshopgamouvaptisis.gr/ — πλαίσιο νέων στην αρχική</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>E-shop / Website</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι η αρχική σας ζητά ακόμα Adobe Flash, που οι browsers δεν το τρέχουν πια — δεν υπάρχει λόγος για άγχος, ένα σύγχρονο e-shop στήνεται πριν τη Black Friday.</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -893,25 +986,40 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=meli-kritiko.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>Το footer γράφει «Copyrights © 2016 - 2018», το site είναι μόνο στα ελληνικά και δεν έχει καλάθι ή checkout.</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>https://www.meli-kritiko.gr/μελι.html — footer και κεντρικό μενού</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>E-shop / Website</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στο meli-kritiko.gr δεν μπορεί κανείς να αγοράσει μέλι online — ένα e-shop με αγγλική έκδοση θα σας άνοιγε και τις παραγγελίες εξωτερικού.</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -956,25 +1064,40 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=gliko-ousia.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>Δεν υπάρχει καλάθι· το site γράφει «Πραγματοποιήστε τις παραγγελίες σας τηλεφωνικά».</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>https://www.gliko-ousia.gr/ — κείμενο παραγγελιών στην αρχική</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>E-shop / Google Ads</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στο site σας οι παραγγελίες γίνονται μόνο τηλεφωνικά — πριν τα χριστουγεννιάτικα δώρα, ένα μικρό e-shop θα σας έφερνε παραγγελίες και εκτός ωραρίου.</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1019,25 +1142,40 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=edia-crete.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>Η ενότητα «Our shop» στην αρχική δείχνει μόνο feed του Instagram· δεν υπάρχει καλάθι, μόνο «Worldwide shipping and wholesale prices available – Contact us».</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>https://edia-crete.gr/ — ενότητα «Our shop» και μενού</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>E-shop / Google Ads</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι το «Our shop» στο site σας είναι feed του Instagram και όχι κατάστημα — θα σας έδειχνα πώς οι επισκέπτες σας θα αγόραζαν το λάδι σας κατευθείαν.</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1082,25 +1220,40 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>Εργαστήριο από το 1983, Αλκιβιάδου 43 (site)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=douroukas.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>Το site είναι μόνο κατάλογος, χωρίς τιμές και καλάθι, και έχει ακόμα banner με alt-text «COVID 19».</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>https://www.douroukas.gr/ — σελίδα «Η Εταιρεία», μενού και banner</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>E-shop / Website</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στο douroukas.gr τα προϊόντα σας δεν αγοράζονται online — κατά την δική μου επαγγελματική άποψη, ένα εργαστήριο από το 1983 αξίζει δικό του e-shop.</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1145,25 +1298,40 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=loukakis-handmade.com&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>Το footer γράφει «Διατηρούνται όλα τα δικαιώματα 2018» και το site είναι μόνο κατάλογος χωρίς τιμές ή καλάθι.</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>https://www.loukakis-handmade.com/ — footer και κεντρικό μενού</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>E-shop / Website</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι το site σας είναι μόνο κατάλογος με footer του 2018 — θα σας πρότεινα ένα site που δείχνει τιμές και δέχεται παραγγελίες για τα έπιπλά σας.</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1208,25 +1376,40 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=lnhandmadesoaps.com&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>Τα κουμπιά «BUY» οδηγούν στο «#» και δεν υπάρχει δικό τους καλάθι· οι πωλήσεις παραπέμπουν σε τρίτα e-shops (jamjar.gr, ecognito.gr κ.ά.).</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>https://www.lnhandmadesoaps.com/ — κουμπιά «BUY» και ενότητα «Online stores»</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>E-shop / Meta Ads</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι τα κουμπιά «BUY» στο site σας δεν οδηγούν πουθενά και οι πελάτες πάνε σε άλλα e-shops — θα σας έδειχνα πώς να κρατάτε εσείς την πώληση.</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1271,25 +1454,40 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>Βιοτεχνία, Μεταμόρφωση (site)</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=epiplo-barela.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>Δεν έχει e-shop: τα προϊόντα έχουν «Δείτε τη συλλογή» χωρίς τιμές και καλάθι, και οι παραγγελίες γίνονται με τηλέφωνο ή email.</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>https://epiplo-barela.gr/ — ενότητα προϊόντων στην αρχική</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>E-shop / Google Ads</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στο epiplo-barela.gr οι συλλογές σας δεν έχουν τιμές ή online παραγγελία — με Google Ads σε ένα e-shop θα σας έβρισκαν όσοι ψάχνουν έπιπλο κατασκευής στην Αττική.</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1334,25 +1532,40 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>Παραγωγική μονάδα, Οινόφυτα (site)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=knossosoap.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>Το site είναι μόνο κατάλογος χωρίς τιμές και καλάθι, και το email στο μπλοκ επικοινωνίας ανοίγει «info@mysite.com» αντί για το πραγματικό.</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>https://www.knossosoap.gr/ — μενού «Our Soaps» και μπλοκ επικοινωνίας</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>E-shop / Website</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι το email στη σελίδα σας ανοίγει το «info@mysite.com» του template — μικρό πράγμα, αλλά σας χάνει μηνύματα· θα σας έδειχνα και πώς θα πουλούσατε online.</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1397,25 +1610,40 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>Επιχείρηση από το 1937 (site)</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=korakis-marinos.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>Δεν υπάρχει e-shop ή καλάθι, και η αρχική δείχνει ακόμα banner COVID που οδηγεί σε PDF του 2021.</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>https://korakis-marinos.gr/ — μενού και banner COVID (site_covid.pdf)</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>E-shop / Meta Ads</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στο site σας τα γλυκά δεν αγοράζονται online και υπάρχει ακόμα banner για τον COVID — πριν τα Χριστούγεννα θα σας πρότεινα e-shop με Meta Ads για δώρα.</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1460,25 +1688,40 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>Κατάστημα, Σεπόλια (site)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=yfanta.com&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>Το footer γράφει «Traditional Home © 2017 all rights reserved» (άλλο όνομα, παλιά χρονιά) και υπάρχει ακόμα εικονίδιο Google+.</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>https://www.yfanta.com/ — footer</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>E-shop / Google Ads</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι το footer του yfanta.com γράφει ακόμα «Traditional Home © 2017» και έχει Google+ — αν σκέφτεστε ανανέωση πριν τη Black Friday, έχω μια ιδέα να σας δείξω.</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1523,25 +1766,40 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>Φυσικό κατάστημα, Τσακάλωφ 32, Κολωνάκι (site)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=ukkalelle.com&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>Το footer γράφει «Ukkalelle Copyright © 2018», ενώ το blog έχει posts του 2025, και στην αρχική δεν υπάρχει εγγραφή σε newsletter.</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>https://ukkalelle.com/en/ — footer της αρχικής</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Website / Meta Ads</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στο site σας δεν υπάρχει εγγραφή σε newsletter — πριν τη Black Friday είναι ο πιο φθηνός τρόπος να ξαναφέρετε πελάτες, και θα σας έδειχνα πώς.</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1586,25 +1844,40 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=psitjewellery.com&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>Στο footer υπάρχει εικόνα με alt «Copyright 2012 Katerina Stamati» και η gallery δεν δείχνει τιμές, μόνο κουμπί «I want it».</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>https://www.psitjewellery.com/ — footer· gallery.php?category=skoularikia</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Website / E-shop</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στη gallery σας τα κοσμήματα δεν έχουν τιμές, μόνο «I want it» — ένα e-shop με τιμές θα έκανε την αγορά δώρου πολύ πιο εύκολη.</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1649,25 +1922,40 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=linum.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>Το footer γράφει «© Copyright 2022» και το link Wishlist οδηγεί σε λάθος διεύθυνση «linum.gr/linum.gr/Wishlist/».</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>https://linum.gr/ — footer και link Wishlist στην κεφαλίδα</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>Website / Meta Ads</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι το link Wishlist στο linum.gr οδηγεί σε λάθος διεύθυνση — μικρό, αλλά πριν τη Black Friday αξίζει έλεγχος· θα σας έστελνα τι άλλο είδα.</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1712,25 +2000,40 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>Εργαστήριο/κατάστημα με ωράριο, Ντεπώ (site)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=pilithos.com&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>Το footer γράφει «©2022 by Pilithos Ceramics» και στην αρχική μένει ανακοίνωση «ΚΑΘΕ ΣΑΒΒΑΤΟ 11:00 - 14:00 ΕΩΣ ΚΑΙ ΤΙΣ 12/9» χωρίς χρονιά.</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>https://www.pilithos.com/ — footer και ενότητα ωραρίου</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Website / E-shop</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στην αρχική σας μένει ακόμα η ανακοίνωση «έως και τις 12/9» — θα σας έδειχνα ένα site που πουλάει τα κεραμικά σας και online.</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1775,25 +2078,40 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=candlelena.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>Η αρχική δίνει δύο όρια δωρεάν αποστολής: το banner λέει 60€ και η ενότητα gift box 50€· footer «Candlelena.gr - 2023».</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>https://candlelena.gr/ — πάνω banner, ενότητα gift box, footer</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Meta Ads / Website</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι η αρχική σας λέει δωρεάν αποστολή στα 60€ στο banner και στα 50€ πιο κάτω — πριν τα δώρα των Χριστουγέννων θα σας πρότεινα να το ξεκαθαρίσουμε μαζί με μια καμπάνια Meta.</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1838,25 +2156,40 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=pelionnaturalsoap.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>Στην ενότητα «ΤΑ ΝΕΑ ΜΑΣ» της αρχικής προβάλλεται ακόμα ως νέο η «Συμμετοχή στην Έκθεση Τροφίμων και Ποτών FoodExpo 2018».</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>https://pelionnaturalsoap.gr/ — ενότητα «ΤΑ ΝΕΑ ΜΑΣ»</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Meta Ads / Google Ads</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι το τελευταίο νέο στην αρχική σας είναι το FoodExpo 2018 — θα σας πρότεινα λίγο φρέσκο περιεχόμενο και μια καμπάνια για τα δώρα των γιορτών.</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1901,25 +2234,40 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=blackmilkcoffee.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
           <t>Το footer γράφει «© BlackMilk 2022» και το link του Facebook είναι χαλασμένο: οδηγεί στο «blackmilkcoffee.gr/www.facebook.com/blackmilkcoffeegreece».</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>https://blackmilkcoffee.gr/ — footer (copyright και εικονίδιο Facebook)</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>Google Ads / Meta Ads</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι το εικονίδιο Facebook στο site σας οδηγεί σε σπασμένη διεύθυνση — μικρή διόρθωση, και μετά θα σας έδειχνα πώς φέρνουμε παραγγελίες συνδρομής με Google Ads.</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1964,25 +2312,40 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=ballsai.com.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>Στο footer τα εικονίδια social είναι κενά links «#» και αντί για copyright της εταιρείας γράφει «© Created by 8theme - Power Elite ThemeForest Author».</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>https://www.ballsai.com.gr/ — footer της αρχικής</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Website / Meta Ads</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στο footer σας γράφει ακόμα το credit του template και τα social εικονίδια δεν οδηγούν πουθενά — θα σας έδειχνα πώς θα δένει το site με το Instagram σας.</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2027,25 +2390,40 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>Φυσικό κατάστημα, Εγνατία 12 (site)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=katakalos-eshop.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>Το footer γράφει «KATAKALOS KIDS FASHION © 2021» και στο μενού, κάτω από «ΧΕΙΜΕΡΙΝΑ», εμφανίζονται «Κολάν Capri» και «Βερμούδα Basic».</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>https://www.katakalos-eshop.gr/ — footer και κεντρικό μενού</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>E-shop / Meta Ads</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι στο μενού «ΧΕΙΜΕΡΙΝΑ» του e-shop σας εμφανίζονται βερμούδες — πριν τη Black Friday θα σας πρότεινα ένα γρήγορο συμμάζεμα και καμπάνια Meta.</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2090,84 +2468,124 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>Φυσικό κατάστημα, 16ης Οκτωβρίου 17, Κατερίνη (site)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>μη ελεγμένο</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=all&amp;ad_type=all&amp;country=GR&amp;q=vaptisi-online.gr&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>Τα τέσσερα εικονίδια social σε header και footer οδηγούν στο placeholder «your_social_link» και το ωράριο διαφέρει (18:00-21:00 στο header, 17:30-20:30 στο footer).</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>https://www.vaptisi-online.gr/ — εικονίδια social σε header και footer</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>Website / Meta Ads</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Είδα ότι τα social εικονίδια στο site σας οδηγούν στο «your_social_link» του template — θα σας έδειχνα πώς να τα συνδέσουμε και να φέρνουμε κόσμο από Meta Ads.</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M26"/>
+  <autoFilter ref="A1:P26"/>
   <dataValidations count="1">
-    <dataValidation sqref="M2:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✅ Ναι,✏️ Αλλαγή,❌ Όχι"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs/leads/2026-10-21.xlsx
+++ b/jobs/leads/2026-10-21.xlsx
@@ -659,12 +659,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210 3219247</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>info@melissinos-art.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Είδα ότι στο site σας τα σανδάλια δεν αγοράζονται online, μόνο με enquiry — κατά την δική μου επαγγελματική άποψη, ένα κανονικό checkout θα σας έφερνε πωλήσεις που τώρα χάνονται πριν τη Black Friday.</t>
+          <t>Στο melissinos-art.com τα σανδάλια παραγγέλνονται μόνο με enquiry, χωρίς τιμή ή καλάθι — θα σας ενδιέφερε να δούμε μαζί πώς θα έμοιαζε ένα απλό checkout πριν τις γιορτές;</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr"/>
@@ -737,12 +737,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27310 81118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>info@esthique.gr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Είδα ότι στο esthique.gr οι παραγγελίες γίνονται μόνο τηλεφωνικά — θα σας πρότεινα ένα απλό e-shop ώστε να πουλάτε και όταν δεν σηκώνετε το τηλέφωνο.</t>
+          <t>Στο esthique.gr οι παραγγελίες γίνονται μόνο τηλεφωνικά — αν σκέφτεστε online πωλήσεις, θα χαρώ να σας δείξω πώς στήνεται ένα απλό e-shop για καλλυντικά.</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Είδα ότι η αρχική σας ζητά ακόμα Adobe Flash, που οι browsers δεν το τρέχουν πια — δεν υπάρχει λόγος για άγχος, ένα σύγχρονο e-shop στήνεται πριν τη Black Friday.</t>
+          <t>Η αρχική του eshopgamouvaptisis.gr ζητά ακόμα Adobe Flash, που οι σημερινοί browsers δεν ανοίγουν — θέλετε να σας στείλουμε πώς φαίνεται σήμερα σε κινητό;</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Είδα ότι στο meli-kritiko.gr δεν μπορεί κανείς να αγοράσει μέλι online — ένα e-shop με αγγλική έκδοση θα σας άνοιγε και τις παραγγελίες εξωτερικού.</t>
+          <t>Στο meli-kritiko.gr δεν υπάρχει καλάθι και το site είναι μόνο στα ελληνικά — έχετε σκεφτεί online πωλήσεις και σε πελάτες του εξωτερικού;</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Είδα ότι στο site σας οι παραγγελίες γίνονται μόνο τηλεφωνικά — πριν τα χριστουγεννιάτικα δώρα, ένα μικρό e-shop θα σας έφερνε παραγγελίες και εκτός ωραρίου.</t>
+          <t>Στο gliko-ousia.gr οι παραγγελίες γίνονται μόνο τηλεφωνικά — αν θέλετε να δέχεστε παραγγελίες online πριν τα Χριστούγεννα, θα χαρώ να σας πω τι χρειάζεται.</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Είδα ότι στο douroukas.gr τα προϊόντα σας δεν αγοράζονται online — κατά την δική μου επαγγελματική άποψη, ένα εργαστήριο από το 1983 αξίζει δικό του e-shop.</t>
+          <t>Στο douroukas.gr τα προϊόντα εμφανίζονται χωρίς τιμές και καλάθι — αν σκέφτεστε e-shop για το εργαστήριο, θα χαρώ να σας δείξω μερικά παραδείγματα.</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Loukakishandmade@gmail.com</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Είδα ότι στο epiplo-barela.gr οι συλλογές σας δεν έχουν τιμές ή online παραγγελία — με Google Ads σε ένα e-shop θα σας έβρισκαν όσοι ψάχνουν έπιπλο κατασκευής στην Αττική.</t>
+          <t>Οι συλλογές στο epiplo-barela.gr δεν έχουν τιμές ούτε online παραγγελία — θα σας ενδιέφερε μια κουβέντα για το πώς σας βρίσκουν όσοι ψάχνουν έπιπλο κατασκευής στην Αττική;</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Είδα ότι το email στη σελίδα σας ανοίγει το «info@mysite.com» του template — μικρό πράγμα, αλλά σας χάνει μηνύματα· θα σας έδειχνα και πώς θα πουλούσατε online.</t>
+          <t>Στη σελίδα σας το post@knossosoap.gr ανοίγει στην πραγματικότητα το «info@mysite.com» του template — σας το επισημαίνω για να διορθωθεί· αν θέλετε, βλέπουμε μαζί και τις online πωλήσεις.</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Είδα ότι στο site σας δεν υπάρχει εγγραφή σε newsletter — πριν τη Black Friday είναι ο πιο φθηνός τρόπος να ξαναφέρετε πελάτες, και θα σας έδειχνα πώς.</t>
+          <t>Στο ukkalelle.com δεν βρήκα φόρμα εγγραφής σε newsletter — θέλετε να συζητήσουμε πώς θα κρατάτε επαφή με τους πελάτες σας πριν τη Black Friday;</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Είδα ότι το εικονίδιο Facebook στο site σας οδηγεί σε σπασμένη διεύθυνση — μικρή διόρθωση, και μετά θα σας έδειχνα πώς φέρνουμε παραγγελίες συνδρομής με Google Ads.</t>
+          <t>Το εικονίδιο Facebook στο blackmilkcoffee.gr οδηγεί σε σπασμένη διεύθυνση — σας το επισημαίνω για να διορθωθεί· αν θέλετε, μιλάμε και για online παραγγελίες.</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr"/>
